--- a/dati_ats.xlsx
+++ b/dati_ats.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\Cruscotto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3D58D0C-E5F9-4C58-B9A4-9550CA48B1EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1066F7E-F866-48F5-AF54-2F60A7997B01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{D1098680-3DF5-4DC8-B205-11DD7C4B5154}"/>
   </bookViews>
   <sheets>
-    <sheet name="Budget" sheetId="1" r:id="rId1"/>
-    <sheet name="Impatto" sheetId="2" r:id="rId2"/>
-    <sheet name="Gantt" sheetId="3" r:id="rId3"/>
+    <sheet name="Budget_FUA" sheetId="1" r:id="rId1"/>
+    <sheet name="Target_LEPS" sheetId="2" r:id="rId2"/>
+    <sheet name="Progetto_Territorio" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
     <t>Voce di Finanziamento</t>
   </si>
@@ -38,9 +38,6 @@
     <t>Budget 2026</t>
   </si>
   <si>
-    <t>FNA</t>
-  </si>
-  <si>
     <t>Domiciliarità</t>
   </si>
   <si>
@@ -53,9 +50,6 @@
     <t>Famiglie PIPPI</t>
   </si>
   <si>
-    <t>Q1</t>
-  </si>
-  <si>
     <t>Task</t>
   </si>
   <si>
@@ -68,7 +62,52 @@
     <t>Completamento</t>
   </si>
   <si>
-    <t>Passaggio consegne</t>
+    <t>FNA (Non Autosufficienza)</t>
+  </si>
+  <si>
+    <t>FNPS (Politiche Sociali)</t>
+  </si>
+  <si>
+    <t>Fondo Povertà (QSFP)</t>
+  </si>
+  <si>
+    <t>PN Inclusione (Progetto CREO)</t>
+  </si>
+  <si>
+    <t>Famiglia e Inclusione</t>
+  </si>
+  <si>
+    <t>Contrasto Povertà</t>
+  </si>
+  <si>
+    <t>Giovani</t>
+  </si>
+  <si>
+    <t>Q1 2026</t>
+  </si>
+  <si>
+    <t>Q2 2026</t>
+  </si>
+  <si>
+    <t>Q3 2026</t>
+  </si>
+  <si>
+    <t>Q4 2026</t>
+  </si>
+  <si>
+    <t>Avvio Centro Servizi "Stazione di Posta" (Baranello)</t>
+  </si>
+  <si>
+    <t>Avvio Spazio Adolescenti "CREO" (Campobasso)</t>
+  </si>
+  <si>
+    <t>Attivazione Programma P.I.P.P.I. (30 Famiglie)</t>
+  </si>
+  <si>
+    <t>Housing per senza dimora (San Giovanni in Galdo)</t>
+  </si>
+  <si>
+    <t>Tirocini di Inclusione Sociale (TIS)</t>
   </si>
 </sst>
 </file>
@@ -421,11 +460,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B274A0E3-4425-48A7-BE8B-D8A8F80F5291}">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.77734375" customWidth="1"/>
-    <col min="2" max="2" width="14.44140625" customWidth="1"/>
+    <col min="1" max="1" width="26.77734375" customWidth="1"/>
+    <col min="2" max="2" width="19.5546875" customWidth="1"/>
     <col min="3" max="3" width="17.44140625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -442,13 +481,46 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
         <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>4</v>
       </c>
       <c r="C2">
         <v>2447200</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3">
+        <v>1244918</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4">
+        <v>1037258</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5">
+        <v>1400934</v>
       </c>
     </row>
   </sheetData>
@@ -458,7 +530,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83766196-9B65-4F09-8367-C839BBA44B59}">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.6640625" customWidth="1"/>
@@ -468,24 +540,57 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" t="s">
         <v>5</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>6</v>
-      </c>
-      <c r="C1" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="B2">
         <v>5</v>
       </c>
       <c r="C2">
         <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3">
+        <v>10</v>
+      </c>
+      <c r="C3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4">
+        <v>14</v>
+      </c>
+      <c r="C4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5">
+        <v>18</v>
+      </c>
+      <c r="C5">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -495,40 +600,97 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{159698EE-62AE-460B-9FE2-1F6E41C9CEE9}">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.77734375" customWidth="1"/>
-    <col min="2" max="3" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="42" customWidth="1"/>
+    <col min="2" max="2" width="26.33203125" customWidth="1"/>
+    <col min="3" max="3" width="10.5546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" t="s">
         <v>9</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" t="s">
         <v>10</v>
-      </c>
-      <c r="C1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="B2" s="1">
-        <v>46078</v>
+        <v>46082</v>
       </c>
       <c r="C2" s="1">
-        <v>46112</v>
+        <v>46203</v>
       </c>
       <c r="D2">
         <v>80</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" s="1">
+        <v>46127</v>
+      </c>
+      <c r="C3" s="1">
+        <v>46295</v>
+      </c>
+      <c r="D3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" s="1">
+        <v>46143</v>
+      </c>
+      <c r="C4" s="1">
+        <v>46356</v>
+      </c>
+      <c r="D4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="1">
+        <v>46174</v>
+      </c>
+      <c r="C5" s="1">
+        <v>46371</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" s="1">
+        <v>46266</v>
+      </c>
+      <c r="C6" s="1">
+        <v>46446</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/dati_ats.xlsx
+++ b/dati_ats.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\Cruscotto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1066F7E-F866-48F5-AF54-2F60A7997B01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6E1336F-77D5-4416-B76C-1A00E67F21C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{D1098680-3DF5-4DC8-B205-11DD7C4B5154}"/>
+    <workbookView xWindow="1488" yWindow="348" windowWidth="7500" windowHeight="10092" firstSheet="2" activeTab="2" xr2:uid="{D1098680-3DF5-4DC8-B205-11DD7C4B5154}"/>
   </bookViews>
   <sheets>
     <sheet name="Budget_FUA" sheetId="1" r:id="rId1"/>
     <sheet name="Target_LEPS" sheetId="2" r:id="rId2"/>
-    <sheet name="Progetto_Territorio" sheetId="3" r:id="rId3"/>
+    <sheet name="Progetti_ATS" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>

--- a/dati_ats.xlsx
+++ b/dati_ats.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\Cruscotto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6E1336F-77D5-4416-B76C-1A00E67F21C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB61B06C-71D0-4FB0-8120-1E65293188CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1488" yWindow="348" windowWidth="7500" windowHeight="10092" firstSheet="2" activeTab="2" xr2:uid="{D1098680-3DF5-4DC8-B205-11DD7C4B5154}"/>
+    <workbookView xWindow="1488" yWindow="348" windowWidth="7500" windowHeight="10092" firstSheet="1" activeTab="1" xr2:uid="{D1098680-3DF5-4DC8-B205-11DD7C4B5154}"/>
   </bookViews>
   <sheets>
     <sheet name="Budget_FUA" sheetId="1" r:id="rId1"/>
@@ -47,9 +47,6 @@
     <t>Assunzioni Assistenti Sociali</t>
   </si>
   <si>
-    <t>Famiglie PIPPI</t>
-  </si>
-  <si>
     <t>Task</t>
   </si>
   <si>
@@ -108,6 +105,9 @@
   </si>
   <si>
     <t>Tirocini di Inclusione Sociale (TIS)</t>
+  </si>
+  <si>
+    <t>Famiglie PIPPI Prese in carico</t>
   </si>
 </sst>
 </file>
@@ -481,7 +481,7 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
@@ -492,10 +492,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C3">
         <v>1244918</v>
@@ -503,10 +503,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C4">
         <v>1037258</v>
@@ -514,10 +514,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C5">
         <v>1400934</v>
@@ -535,7 +535,7 @@
   <cols>
     <col min="1" max="1" width="12.6640625" customWidth="1"/>
     <col min="2" max="2" width="26.77734375" customWidth="1"/>
-    <col min="3" max="3" width="17.77734375" customWidth="1"/>
+    <col min="3" max="3" width="21.21875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
@@ -546,12 +546,12 @@
         <v>5</v>
       </c>
       <c r="C1" t="s">
-        <v>6</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B2">
         <v>5</v>
@@ -562,7 +562,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B3">
         <v>10</v>
@@ -573,7 +573,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B4">
         <v>14</v>
@@ -584,7 +584,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B5">
         <v>18</v>
@@ -611,21 +611,21 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" t="s">
         <v>7</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>8</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>9</v>
-      </c>
-      <c r="D1" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B2" s="1">
         <v>46082</v>
@@ -639,7 +639,7 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B3" s="1">
         <v>46127</v>
@@ -653,7 +653,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B4" s="1">
         <v>46143</v>
@@ -667,7 +667,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B5" s="1">
         <v>46174</v>
@@ -681,7 +681,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B6" s="1">
         <v>46266</v>

--- a/dati_ats.xlsx
+++ b/dati_ats.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\Cruscotto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB61B06C-71D0-4FB0-8120-1E65293188CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89528B79-918F-4A3C-AF10-47445932EE44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1488" yWindow="348" windowWidth="7500" windowHeight="10092" firstSheet="1" activeTab="1" xr2:uid="{D1098680-3DF5-4DC8-B205-11DD7C4B5154}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{D1098680-3DF5-4DC8-B205-11DD7C4B5154}"/>
   </bookViews>
   <sheets>
     <sheet name="Budget_FUA" sheetId="1" r:id="rId1"/>
     <sheet name="Target_LEPS" sheetId="2" r:id="rId2"/>
     <sheet name="Progetti_ATS" sheetId="3" r:id="rId3"/>
+    <sheet name="Pipeline_Bandi" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
   <si>
     <t>Voce di Finanziamento</t>
   </si>
@@ -108,6 +109,57 @@
   </si>
   <si>
     <t>Famiglie PIPPI Prese in carico</t>
+  </si>
+  <si>
+    <t>Nome Bando / Progetto</t>
+  </si>
+  <si>
+    <t>Ente Erogatore (Fondo)</t>
+  </si>
+  <si>
+    <t>Scadenza</t>
+  </si>
+  <si>
+    <t>Budget Richiesto (€)</t>
+  </si>
+  <si>
+    <t>Stato</t>
+  </si>
+  <si>
+    <t>Avviso Inclusione Giovani</t>
+  </si>
+  <si>
+    <t>Bando Povertà Educativa</t>
+  </si>
+  <si>
+    <t>Potenziamento Domiciliarità</t>
+  </si>
+  <si>
+    <t>Prevenzione Violenza Genere</t>
+  </si>
+  <si>
+    <t>PR Molise FSE+</t>
+  </si>
+  <si>
+    <t>Impresa Sociale Con i Bambini</t>
+  </si>
+  <si>
+    <t>PNRR M5C2</t>
+  </si>
+  <si>
+    <t>Commissione UE (CERV)</t>
+  </si>
+  <si>
+    <t>In scrittura</t>
+  </si>
+  <si>
+    <t>Analisi fattibilità</t>
+  </si>
+  <si>
+    <t>Inviato</t>
+  </si>
+  <si>
+    <t>Da valutare</t>
   </si>
 </sst>
 </file>
@@ -696,4 +748,106 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CAD737B-0BC4-4FBF-A775-EA2D40DA63EA}">
+  <dimension ref="A10:E14"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="26.88671875" customWidth="1"/>
+    <col min="2" max="2" width="26.44140625" customWidth="1"/>
+    <col min="3" max="3" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.6640625" customWidth="1"/>
+    <col min="5" max="5" width="11.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" t="s">
+        <v>29</v>
+      </c>
+      <c r="D10" t="s">
+        <v>30</v>
+      </c>
+      <c r="E10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="1">
+        <v>46157</v>
+      </c>
+      <c r="D11">
+        <v>250000</v>
+      </c>
+      <c r="E11" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" t="s">
+        <v>37</v>
+      </c>
+      <c r="C12" s="1">
+        <v>46203</v>
+      </c>
+      <c r="D12">
+        <v>400000</v>
+      </c>
+      <c r="E12" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" t="s">
+        <v>38</v>
+      </c>
+      <c r="C13" s="1">
+        <v>46122</v>
+      </c>
+      <c r="D13">
+        <v>180000</v>
+      </c>
+      <c r="E13" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" t="s">
+        <v>39</v>
+      </c>
+      <c r="C14" s="1">
+        <v>46266</v>
+      </c>
+      <c r="D14">
+        <v>350000</v>
+      </c>
+      <c r="E14" t="s">
+        <v>43</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/dati_ats.xlsx
+++ b/dati_ats.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\Cruscotto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89528B79-918F-4A3C-AF10-47445932EE44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3474C649-E616-46F5-A29E-ACB6321FEE74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{D1098680-3DF5-4DC8-B205-11DD7C4B5154}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{D1098680-3DF5-4DC8-B205-11DD7C4B5154}"/>
   </bookViews>
   <sheets>
     <sheet name="Budget_FUA" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="49">
   <si>
     <t>Voce di Finanziamento</t>
   </si>
@@ -160,6 +160,21 @@
   </si>
   <si>
     <t>Da valutare</t>
+  </si>
+  <si>
+    <t>SDG_Agenda2030</t>
+  </si>
+  <si>
+    <t>Budget</t>
+  </si>
+  <si>
+    <t>SDG 1 - Povertà</t>
+  </si>
+  <si>
+    <t>SDG 4 - Istruzione</t>
+  </si>
+  <si>
+    <t>SDG 8 - Lavoro</t>
   </si>
 </sst>
 </file>
@@ -652,16 +667,17 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{159698EE-62AE-460B-9FE2-1F6E41C9CEE9}">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
     <col min="2" max="2" width="26.33203125" customWidth="1"/>
     <col min="3" max="3" width="10.5546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18" customWidth="1"/>
+    <col min="5" max="5" width="17.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -674,8 +690,14 @@
       <c r="D1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>21</v>
       </c>
@@ -688,8 +710,14 @@
       <c r="D2">
         <v>80</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2">
+        <v>45000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>22</v>
       </c>
@@ -702,8 +730,14 @@
       <c r="D3">
         <v>30</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F3">
+        <v>1400934</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>23</v>
       </c>
@@ -716,8 +750,14 @@
       <c r="D4">
         <v>15</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E4" t="s">
+        <v>46</v>
+      </c>
+      <c r="F4">
+        <v>140284</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>24</v>
       </c>
@@ -730,8 +770,14 @@
       <c r="D5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F5">
+        <v>114000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>25</v>
       </c>
@@ -743,6 +789,12 @@
       </c>
       <c r="D6">
         <v>0</v>
+      </c>
+      <c r="E6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F6">
+        <v>387833</v>
       </c>
     </row>
   </sheetData>
